--- a/artfynd/A 35214-2026 artfynd.xlsx
+++ b/artfynd/A 35214-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135855636</v>
       </c>
       <c r="B2" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35214-2026 artfynd.xlsx
+++ b/artfynd/A 35214-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135855636</v>
+        <v>136194227</v>
       </c>
       <c r="B2" t="n">
-        <v>92086</v>
+        <v>93357</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>754772</v>
+        <v>754807</v>
       </c>
       <c r="R2" t="n">
-        <v>7316156</v>
+        <v>7316184</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,19 +752,9 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>07:59</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>07:59</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -795,13 +785,471 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136194227</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135855636</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92086</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Vidsel, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>754772</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7316156</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135855636</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136194230</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92086</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vidsel, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>754769</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7316166</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136194230</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136194229</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80564</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vidsel, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>754765</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7316146</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136194229</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136194228</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79202</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vidsel, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>754801</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7316156</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136194228</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35214-2026 artfynd.xlsx
+++ b/artfynd/A 35214-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194227</v>
       </c>
       <c r="B2" t="n">
-        <v>93357</v>
+        <v>93358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135855636</v>
       </c>
       <c r="B3" t="n">
-        <v>92086</v>
+        <v>92087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136194230</v>
       </c>
       <c r="B4" t="n">
-        <v>92086</v>
+        <v>92087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35214-2026 artfynd.xlsx
+++ b/artfynd/A 35214-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194227</v>
       </c>
       <c r="B2" t="n">
-        <v>93358</v>
+        <v>93359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135855636</v>
       </c>
       <c r="B3" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136194230</v>
       </c>
       <c r="B4" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136194229</v>
       </c>
       <c r="B5" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136194228</v>
       </c>
       <c r="B6" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35214-2026 artfynd.xlsx
+++ b/artfynd/A 35214-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194227</v>
       </c>
       <c r="B2" t="n">
-        <v>93359</v>
+        <v>93365</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135855636</v>
       </c>
       <c r="B3" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136194230</v>
       </c>
       <c r="B4" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136194229</v>
       </c>
       <c r="B5" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136194228</v>
       </c>
       <c r="B6" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35214-2026 artfynd.xlsx
+++ b/artfynd/A 35214-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194227</v>
       </c>
       <c r="B2" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135855636</v>
       </c>
       <c r="B3" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136194230</v>
       </c>
       <c r="B4" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136194229</v>
       </c>
       <c r="B5" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136194228</v>
       </c>
       <c r="B6" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
